--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487604_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487604_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6756</v>
+        <v>3.542</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4054</v>
+        <v>2.3263</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2702</v>
+        <v>1.2157</v>
       </c>
       <c r="G2" t="n">
         <v>0.4252</v>
@@ -610,13 +610,13 @@
         <v>1.9403</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3392</v>
+        <v>-0.4727</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2412</v>
+        <v>-0.3202</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.098</v>
+        <v>-0.1525</v>
       </c>
       <c r="V2" t="n">
         <v>1.6493</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9164</v>
+        <v>1.0765</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5262</v>
+        <v>-0.6659</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4426</v>
+        <v>1.7424</v>
       </c>
       <c r="G3" t="n">
         <v>0.0245</v>
@@ -688,13 +688,13 @@
         <v>4.2687</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4365</v>
+        <v>-1.2763</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.125</v>
+        <v>-1.2646</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3115</v>
+        <v>-0.0117</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2626</v>
+        <v>0.5234</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1887</v>
+        <v>0.0566</v>
       </c>
       <c r="G4" t="n">
         <v>0.2</v>
@@ -766,13 +766,13 @@
         <v>2.7164</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6187</v>
+        <v>-1.1126</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2472</v>
+        <v>-0.9865</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3714</v>
+        <v>-0.1261</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2239</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. BUHORSKYI</t>
+          <t>P. BARCALA BELTRAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2612</v>
+        <v>-0.6891</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8113</v>
+        <v>-3.1633</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4499</v>
+        <v>2.4742</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1264</v>
+        <v>0.5148</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3989</v>
+        <v>-0.29</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2725</v>
+        <v>0.8048</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3068</v>
+        <v>2.6771</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3068</v>
+        <v>1.7054</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.9716</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1804</v>
+        <v>-2.1623</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9079</v>
+        <v>-1.9954</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2725</v>
+        <v>-0.1669</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5523</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9105</v>
+        <v>-5.821</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3582</v>
+        <v>4.0747</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3885</v>
+        <v>-1.7188</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1222</v>
+        <v>-1.5254</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2663</v>
+        <v>-0.1934</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2239</v>
+        <v>2.2612</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3299</v>
+        <v>1.506</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.894</v>
+        <v>0.7553</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ SANCHEZ</t>
+          <t>D. BUHORSKYI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8474</v>
+        <v>-1.4464</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.4962</v>
+        <v>-1.051</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6488</v>
+        <v>-0.3954</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.1944</v>
+        <v>1.1264</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1584</v>
+        <v>1.3989</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.3528</v>
+        <v>-0.2725</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1831</v>
+        <v>2.3068</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4634</v>
+        <v>2.3068</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.6465</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0114</v>
+        <v>-1.1804</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.305</v>
+        <v>-0.9079</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7063</v>
+        <v>-0.2725</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.194</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.8806</v>
+        <v>-2.9105</v>
       </c>
       <c r="R6" t="n">
-        <v>3.6866</v>
+        <v>1.3582</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1514</v>
+        <v>0.2033</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.125</v>
+        <v>-0.1175</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0264</v>
+        <v>0.3208</v>
       </c>
       <c r="V6" t="n">
-        <v>1.6925</v>
+        <v>-1.2239</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6925</v>
+        <v>-0.3299</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. BARCALA BELTRAN</t>
+          <t>L. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9465</v>
+        <v>-1.5599</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.6848</v>
+        <v>-3.5358</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7383</v>
+        <v>1.9759</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5148</v>
+        <v>-2.1944</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.29</v>
+        <v>1.1584</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8048</v>
+        <v>-3.3528</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6771</v>
+        <v>-0.1831</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7054</v>
+        <v>2.4634</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9716</v>
+        <v>-2.6465</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1623</v>
+        <v>-2.0114</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.9954</v>
+        <v>-1.305</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1669</v>
+        <v>-0.7063</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.7463</v>
+        <v>-0.194</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.821</v>
+        <v>-3.8806</v>
       </c>
       <c r="R7" t="n">
-        <v>4.0747</v>
+        <v>3.6866</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.9762</v>
+        <v>-0.8639</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.0469</v>
+        <v>-1.1645</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9293</v>
+        <v>0.3006</v>
       </c>
       <c r="V7" t="n">
-        <v>2.2612</v>
+        <v>1.6925</v>
       </c>
       <c r="W7" t="n">
-        <v>1.506</v>
+        <v>1.6925</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.7768</v>
+        <v>-4.9676</v>
       </c>
       <c r="E8" t="n">
         <v>-4.608</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1689</v>
+        <v>-0.3597</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9213</v>
@@ -1078,13 +1078,13 @@
         <v>0.3881</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2968</v>
+        <v>0.106</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1088</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4056</v>
+        <v>0.2148</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6597</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-9.208299999999999</v>
+        <v>-10.3043</v>
       </c>
       <c r="E9" t="n">
-        <v>-11.4577</v>
+        <v>-11.1364</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2494</v>
+        <v>0.8321</v>
       </c>
       <c r="G9" t="n">
         <v>-11.8062</v>
@@ -1156,13 +1156,13 @@
         <v>2.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0157</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.4289</v>
+        <v>-1.1076</v>
       </c>
       <c r="U9" t="n">
-        <v>2.4447</v>
+        <v>1.0274</v>
       </c>
       <c r="V9" t="n">
         <v>0.6119</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-14.3743</v>
+        <v>-13.7688</v>
       </c>
       <c r="E10" t="n">
-        <v>-21.9162</v>
+        <v>-21.3107</v>
       </c>
       <c r="F10" t="n">
-        <v>7.541800000000001</v>
+        <v>7.5418</v>
       </c>
       <c r="G10" t="n">
         <v>-12.631</v>
@@ -1207,7 +1207,7 @@
         <v>-6.089499999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4569000000000001</v>
+        <v>-0.456900000000001</v>
       </c>
       <c r="K10" t="n">
         <v>2.7683</v>
@@ -1234,13 +1234,13 @@
         <v>21.3435</v>
       </c>
       <c r="S10" t="n">
-        <v>-5.821</v>
+        <v>-5.215200000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-7.2008</v>
+        <v>-6.5951</v>
       </c>
       <c r="U10" t="n">
-        <v>1.38</v>
+        <v>1.3799</v>
       </c>
       <c r="V10" t="n">
         <v>3.1074</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.202</v>
+        <v>7.0695</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8814</v>
+        <v>2.482</v>
       </c>
       <c r="F11" t="n">
-        <v>4.3206</v>
+        <v>4.5875</v>
       </c>
       <c r="G11" t="n">
         <v>5.8362</v>
@@ -1312,13 +1312,13 @@
         <v>2.3284</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3522</v>
+        <v>0.5154</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8479</v>
+        <v>-0.2473</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4958</v>
+        <v>0.7627</v>
       </c>
       <c r="V11" t="n">
         <v>0.3299</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.9876</v>
+        <v>4.7751</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9165</v>
+        <v>1.5162</v>
       </c>
       <c r="F12" t="n">
-        <v>3.071</v>
+        <v>3.259</v>
       </c>
       <c r="G12" t="n">
         <v>1.5248</v>
@@ -1390,13 +1390,13 @@
         <v>2.7164</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1523</v>
+        <v>0.9399</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3174</v>
+        <v>-0.083</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8349</v>
+        <v>1.0229</v>
       </c>
       <c r="V12" t="n">
         <v>0.5642</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8188</v>
+        <v>3.8282</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3629</v>
+        <v>3.5631</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4559</v>
+        <v>0.2651</v>
       </c>
       <c r="G13" t="n">
         <v>0.9555</v>
@@ -1468,13 +1468,13 @@
         <v>0.5821</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1633</v>
+        <v>0.1727</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4845</v>
+        <v>-0.2843</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6478</v>
+        <v>0.4571</v>
       </c>
       <c r="V13" t="n">
         <v>2.1179</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5167</v>
+        <v>3.3861</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3388</v>
+        <v>-0.0616</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1779</v>
+        <v>3.4476</v>
       </c>
       <c r="G14" t="n">
         <v>1.6179</v>
@@ -1546,13 +1546,13 @@
         <v>1.9403</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9286</v>
+        <v>0.798</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4991</v>
+        <v>0.0987</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4296</v>
+        <v>0.6993</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3636</v>
+        <v>1.3086</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2801</v>
+        <v>-0.0202</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0836</v>
+        <v>1.3288</v>
       </c>
       <c r="G15" t="n">
         <v>2.9497</v>
@@ -1624,13 +1624,13 @@
         <v>1.5523</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0065</v>
+        <v>-0.0485</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1222</v>
+        <v>-0.1781</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1157</v>
+        <v>0.1296</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2343</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1282</v>
+        <v>0.5887</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.4728</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2006</v>
+        <v>1.0615</v>
       </c>
       <c r="G16" t="n">
         <v>1.2253</v>
@@ -1702,13 +1702,13 @@
         <v>0.9702</v>
       </c>
       <c r="S16" t="n">
-        <v>1.079</v>
+        <v>0.5395</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2557</v>
+        <v>-0.1447</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8233</v>
+        <v>0.6842</v>
       </c>
       <c r="V16" t="n">
         <v>-1.1761</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. BARROS CONDES</t>
+          <t>D. TOLOSA OROPESA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1016</v>
+        <v>0.3006</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.7577</v>
+        <v>-0.4946</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6561</v>
+        <v>0.7952</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2717</v>
+        <v>2.627</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0708</v>
+        <v>0.4119</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3426</v>
+        <v>2.215</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1192</v>
+        <v>2.6114</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6014</v>
+        <v>0.1071</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7207</v>
+        <v>2.5043</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1525</v>
+        <v>0.0156</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5306</v>
+        <v>0.3048</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3781</v>
+        <v>-0.2892</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.194</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.9105</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7164</v>
+        <v>2.1344</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5776</v>
+        <v>0.8975</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5915</v>
+        <v>-0.1955</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9861</v>
+        <v>1.093</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.2134</v>
+        <v>-2.4477</v>
       </c>
       <c r="W17" t="n">
-        <v>-1.3194</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.894</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8079</v>
+        <v>-0.165</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0589</v>
+        <v>-1.6585</v>
       </c>
       <c r="F18" t="n">
-        <v>1.251</v>
+        <v>1.4935</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5153</v>
@@ -1858,13 +1858,13 @@
         <v>1.3582</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3031</v>
+        <v>0.3398</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7145</v>
+        <v>-0.3141</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4114</v>
+        <v>0.6539</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3776</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. TOLOSA OROPESA</t>
+          <t>M. BATLLE BERNARDO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8578</v>
+        <v>-0.5904</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1953</v>
+        <v>-1.3683</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3375</v>
+        <v>0.7779</v>
       </c>
       <c r="G19" t="n">
-        <v>2.627</v>
+        <v>-0.9645</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4119</v>
+        <v>1.6865</v>
       </c>
       <c r="I19" t="n">
-        <v>2.215</v>
+        <v>-2.651</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6114</v>
+        <v>-0.2519</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1071</v>
+        <v>1.7095</v>
       </c>
       <c r="L19" t="n">
-        <v>2.5043</v>
+        <v>-1.9614</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0156</v>
+        <v>-0.7127</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3048</v>
+        <v>-0.0231</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2892</v>
+        <v>-0.6896</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7761</v>
+        <v>0.3881</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1344</v>
+        <v>1.3582</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2609</v>
+        <v>0.3637</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8962</v>
+        <v>-0.0508</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6353</v>
+        <v>0.4144</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.4477</v>
+        <v>-0.3776</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.0955</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4477</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. BATLLE BERNARDO</t>
+          <t>C. BARROS CONDES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0815</v>
+        <v>-1.2422</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6686</v>
+        <v>-4.059</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5871</v>
+        <v>2.8168</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9645</v>
+        <v>-0.2717</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6865</v>
+        <v>0.0708</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.651</v>
+        <v>-0.3426</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2519</v>
+        <v>-0.1192</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7095</v>
+        <v>0.6014</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9614</v>
+        <v>-0.7207</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7127</v>
+        <v>-0.1525</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0231</v>
+        <v>-0.5306</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6896</v>
+        <v>0.3781</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3881</v>
+        <v>-0.194</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3582</v>
+        <v>2.7164</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1274</v>
+        <v>1.437</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3511</v>
+        <v>0.2902</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2237</v>
+        <v>1.1468</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3776</v>
+        <v>-2.2134</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.0955</v>
+        <v>-1.3194</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2821</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.607</v>
+        <v>-1.5342</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4742</v>
+        <v>-2.3741</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8672</v>
+        <v>0.8399</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1402</v>
@@ -2092,13 +2092,13 @@
         <v>0.3881</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1153</v>
+        <v>0.1881</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1694</v>
+        <v>-0.0693</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2847</v>
+        <v>0.2574</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1866</v>
+        <v>-2.016</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.4244</v>
+        <v>-4.9239</v>
       </c>
       <c r="F22" t="n">
-        <v>3.2377</v>
+        <v>2.9079</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2136</v>
@@ -2170,13 +2170,13 @@
         <v>2.3284</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8419</v>
+        <v>1.0125</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-0.2016</v>
       </c>
       <c r="U22" t="n">
-        <v>1.544</v>
+        <v>1.2141</v>
       </c>
       <c r="V22" t="n">
         <v>0.7075</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>14.3745</v>
+        <v>15.709</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.8718</v>
+        <v>-7.8717</v>
       </c>
       <c r="F23" t="n">
-        <v>22.2462</v>
+        <v>23.5807</v>
       </c>
       <c r="G23" t="n">
         <v>12.6311</v>
@@ -2218,19 +2218,19 @@
         <v>6.541500000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>6.0895</v>
+        <v>6.089500000000001</v>
       </c>
       <c r="J23" t="n">
         <v>12.174</v>
       </c>
       <c r="K23" t="n">
-        <v>9.309800000000003</v>
+        <v>9.309800000000001</v>
       </c>
       <c r="L23" t="n">
         <v>2.864299999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4568000000000004</v>
+        <v>0.4568000000000003</v>
       </c>
       <c r="N23" t="n">
         <v>-2.7684</v>
@@ -2248,13 +2248,13 @@
         <v>20.3734</v>
       </c>
       <c r="S23" t="n">
-        <v>5.820899999999999</v>
+        <v>7.1556</v>
       </c>
       <c r="T23" t="n">
         <v>-1.3798</v>
       </c>
       <c r="U23" t="n">
-        <v>7.200900000000001</v>
+        <v>8.535399999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-3.1072</v>
